--- a/data/trans_orig/P1415-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2012</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>27892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25972</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>51616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>942546</t>
+          <t>943265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>963061</t>
+          <t>962392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1309102</t>
+          <t>1309905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1327626</t>
+          <t>1328539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2260869</t>
+          <t>2260824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2286468</t>
+          <t>2286145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>40903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22625</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29785</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56381</t>
+          <t>57905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1922371</t>
+          <t>1923054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1945376</t>
+          <t>1945052</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1731967</t>
+          <t>1731345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1747565</t>
+          <t>1746730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3662168</t>
+          <t>3660644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3688764</t>
+          <t>3688303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>26094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460802</t>
+          <t>460701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477895</t>
+          <t>477644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446305</t>
+          <t>445467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456649</t>
+          <t>456506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>914099</t>
+          <t>913719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932474</t>
+          <t>931992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>43378</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76328</t>
+          <t>77558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26748</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51365</t>
+          <t>50856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76578</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116391</t>
+          <t>116516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3343454</t>
+          <t>3342224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3377705</t>
+          <t>3376404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3499655</t>
+          <t>3500164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3524272</t>
+          <t>3525466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6854410</t>
+          <t>6854285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6894223</t>
+          <t>6895031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2016</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40402</t>
+          <t>41818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>738456</t>
+          <t>738635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>749939</t>
+          <t>749603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>962970</t>
+          <t>962446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>982958</t>
+          <t>981761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1708605</t>
+          <t>1707189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1730134</t>
+          <t>1730251</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13276</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>32173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>21507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44055</t>
+          <t>44370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>39488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68220</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2045189</t>
+          <t>2044212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2063109</t>
+          <t>2062961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1944245</t>
+          <t>1943930</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1967237</t>
+          <t>1966793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3996465</t>
+          <t>3996997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4025127</t>
+          <t>4025197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532791</t>
+          <t>534338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544585</t>
+          <t>545062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537833</t>
+          <t>537533</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>547192</t>
+          <t>547224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076577</t>
+          <t>1076829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090168</t>
+          <t>1090641</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25219</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>47501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>42120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72769</t>
+          <t>72989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74523</t>
+          <t>73155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113137</t>
+          <t>113069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3327444</t>
+          <t>3330117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3352399</t>
+          <t>3352842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3459331</t>
+          <t>3459111</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3489041</t>
+          <t>3489980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6796581</t>
+          <t>6796649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6835195</t>
+          <t>6836563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1415-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31378</t>
+          <t>31255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51616</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>943265</t>
+          <t>943388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>962392</t>
+          <t>962723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1309905</t>
+          <t>1309878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1328539</t>
+          <t>1327717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2260824</t>
+          <t>2260877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2286145</t>
+          <t>2286104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40903</t>
+          <t>39701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57905</t>
+          <t>55227</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1923054</t>
+          <t>1924256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1945052</t>
+          <t>1945265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1731345</t>
+          <t>1732181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1746730</t>
+          <t>1747193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3660644</t>
+          <t>3663322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3688303</t>
+          <t>3688719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460701</t>
+          <t>461441</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477644</t>
+          <t>477950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445467</t>
+          <t>445665</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456506</t>
+          <t>456587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>913719</t>
+          <t>913494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>931992</t>
+          <t>932254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43378</t>
+          <t>42765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77558</t>
+          <t>75880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50856</t>
+          <t>52057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75770</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116516</t>
+          <t>116112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3342224</t>
+          <t>3343902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3376404</t>
+          <t>3377017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3500164</t>
+          <t>3498963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3525466</t>
+          <t>3524046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6854285</t>
+          <t>6854689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6895031</t>
+          <t>6894536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41818</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>738635</t>
+          <t>737963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>749603</t>
+          <t>749870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>962446</t>
+          <t>962598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>981761</t>
+          <t>983113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1707189</t>
+          <t>1707157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1730251</t>
+          <t>1729192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32173</t>
+          <t>31459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>22893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44370</t>
+          <t>44388</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39488</t>
+          <t>37269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67688</t>
+          <t>67042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2044212</t>
+          <t>2044926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2062961</t>
+          <t>2062841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1943930</t>
+          <t>1943912</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1966793</t>
+          <t>1965407</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3996997</t>
+          <t>3997643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4025197</t>
+          <t>4027416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,47 +3035,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4944</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11289</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4944</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11607</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534338</t>
+          <t>532456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545062</t>
+          <t>544651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,49 +3148,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>544196</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>537851</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>547301</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>544196</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>537533</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>547224</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1017</t>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076829</t>
+          <t>1077518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090641</t>
+          <t>1090381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24776</t>
+          <t>24928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47501</t>
+          <t>47993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42120</t>
+          <t>42619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72989</t>
+          <t>73257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73155</t>
+          <t>73840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113069</t>
+          <t>113916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3330117</t>
+          <t>3329625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3352842</t>
+          <t>3352690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3459111</t>
+          <t>3458843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3489980</t>
+          <t>3489481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6796649</t>
+          <t>6795802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6836563</t>
+          <t>6835878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
